--- a/docs/StructureDefinition-HAHVisitEncounter.xlsx
+++ b/docs/StructureDefinition-HAHVisitEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T17:33:17+08:00</t>
+    <t>2026-09-29T04:34:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>每次實地、視訊或電話評估建立一筆訪視，參照整段照護與收案療程。預約或通知不能當成已完成訪視。</t>
+    <t>每次實地、視訊或電話評估建立一筆訪視，參照整段照護與收案療程。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -808,10 +808,7 @@
     <t>病人就醫分類的概念，例如：門診病人、住院病人、急診病人、居家照護或其他因地方不同而產生的概念。</t>
   </si>
   <si>
-    <t>就醫的分類；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -853,9 +850,6 @@
   <si>
     <t>inpatient ｜ outpatient ｜ ambulatory ｜ emergency +.
 住院病人 ｜ 門診病人 ｜ 非臥床（可行走）病人醫療服務 ｜ 急診 +</t>
-  </si>
-  <si>
-    <t>就醫類別；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -1222,10 +1216,7 @@
     <t>表明就醫的急迫性</t>
   </si>
   <si>
-    <t>表明就醫的迫切性；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1716,10 +1707,7 @@
     <t>此次住院是否為再入院，如果知道的話，請說明原因。</t>
   </si>
   <si>
-    <t>這次住院就醫的再入院原因；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092|3.0.0</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -2268,17 +2256,17 @@
   <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.16015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.83984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.52734375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.47265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="27.953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="230.44140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="230.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2287,26 +2275,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="125.0625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.16015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="125.8359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.20703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.47265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="163.86328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="161.73828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5448,11 +5436,9 @@
       <c r="X28" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5488,21 +5474,21 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5528,10 +5514,10 @@
         <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5582,7 +5568,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5611,10 +5597,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5723,10 +5709,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5837,10 +5823,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5953,10 +5939,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5979,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6014,11 +6000,9 @@
       <c r="X33" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y33" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -6036,7 +6020,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -6065,10 +6049,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6094,10 +6078,10 @@
         <v>210</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6148,7 +6132,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -6177,10 +6161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6206,13 +6190,13 @@
         <v>182</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6223,29 +6207,29 @@
         <v>20</v>
       </c>
       <c r="S35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="T35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="Y35" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
       </c>
@@ -6262,7 +6246,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6277,24 +6261,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6320,10 +6304,10 @@
         <v>182</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6350,13 +6334,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6374,7 +6358,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6389,7 +6373,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>165</v>
@@ -6398,15 +6382,15 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6432,10 +6416,10 @@
         <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6515,10 +6499,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6544,10 +6528,10 @@
         <v>133</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6627,10 +6611,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6656,16 +6640,16 @@
         <v>251</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6702,7 +6686,7 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
@@ -6712,7 +6696,7 @@
         <v>137</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6730,24 +6714,24 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
@@ -6772,16 +6756,16 @@
         <v>251</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6810,7 +6794,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6828,7 +6812,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6846,21 +6830,21 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6886,10 +6870,10 @@
         <v>161</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6969,10 +6953,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6998,13 +6982,13 @@
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7083,10 +7067,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7112,16 +7096,16 @@
         <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7131,7 +7115,7 @@
         <v>20</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>20</v>
@@ -7170,7 +7154,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7188,21 +7172,21 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7228,13 +7212,13 @@
         <v>161</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7284,7 +7268,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7302,21 +7286,21 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7342,14 +7326,14 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7398,7 +7382,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7416,21 +7400,21 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7456,14 +7440,14 @@
         <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7512,7 +7496,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7530,21 +7514,21 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7567,19 +7551,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7628,7 +7612,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7646,24 +7630,24 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7688,16 +7672,16 @@
         <v>251</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7726,7 +7710,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7744,7 +7728,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7762,21 +7746,21 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7802,10 +7786,10 @@
         <v>161</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7885,10 +7869,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7914,13 +7898,13 @@
         <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7999,10 +7983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8028,16 +8012,16 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8047,7 +8031,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -8086,7 +8070,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8104,21 +8088,21 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8144,13 +8128,13 @@
         <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8200,7 +8184,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8218,21 +8202,21 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8258,14 +8242,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8314,7 +8298,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8332,21 +8316,21 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8372,14 +8356,14 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8428,7 +8412,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8446,21 +8430,21 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8483,19 +8467,19 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8544,7 +8528,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8562,24 +8546,24 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8604,16 +8588,16 @@
         <v>251</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8642,7 +8626,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8660,7 +8644,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8678,21 +8662,21 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8718,10 +8702,10 @@
         <v>161</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8801,10 +8785,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8830,13 +8814,13 @@
         <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8915,10 +8899,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8944,16 +8928,16 @@
         <v>101</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8963,7 +8947,7 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>20</v>
@@ -9002,7 +8986,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9020,21 +9004,21 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9060,13 +9044,13 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9116,7 +9100,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9134,21 +9118,21 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9174,14 +9158,14 @@
         <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9230,7 +9214,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9248,21 +9232,21 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9288,14 +9272,14 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9344,7 +9328,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9362,21 +9346,21 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9399,19 +9383,19 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9460,7 +9444,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9478,21 +9462,21 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9518,16 +9502,16 @@
         <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9576,7 +9560,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9594,21 +9578,21 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9634,10 +9618,10 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9664,13 +9648,11 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9688,7 +9670,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9706,25 +9688,25 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9743,16 +9725,16 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9802,7 +9784,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9817,24 +9799,24 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9857,13 +9839,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9914,7 +9896,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9929,28 +9911,28 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>165</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9969,13 +9951,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10026,7 +10008,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10041,10 +10023,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -10055,10 +10037,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10084,10 +10066,10 @@
         <v>235</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10138,7 +10120,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10153,24 +10135,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10279,10 +10261,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10393,10 +10375,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10509,10 +10491,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10538,13 +10520,13 @@
         <v>182</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10573,10 +10555,10 @@
         <v>187</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10594,7 +10576,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10609,24 +10591,24 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10652,10 +10634,10 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10706,7 +10688,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10724,21 +10706,21 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10761,13 +10743,13 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10818,7 +10800,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10833,24 +10815,24 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10873,13 +10855,13 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10930,7 +10912,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10945,24 +10927,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10988,13 +10970,13 @@
         <v>210</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11044,7 +11026,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11059,24 +11041,24 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>457</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11185,10 +11167,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11299,10 +11281,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11325,16 +11307,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11384,7 +11366,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11393,7 +11375,7 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
@@ -11402,21 +11384,21 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11439,23 +11421,23 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q81" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="R81" t="s" s="2">
         <v>20</v>
@@ -11500,7 +11482,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11509,7 +11491,7 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>99</v>
@@ -11518,21 +11500,21 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11555,16 +11537,16 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11614,7 +11596,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11629,28 +11611,28 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11672,13 +11654,13 @@
         <v>182</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11707,10 +11689,10 @@
         <v>112</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -11728,7 +11710,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11743,28 +11725,28 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>494</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11783,16 +11765,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11842,7 +11824,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11857,24 +11839,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>494</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11900,10 +11882,10 @@
         <v>235</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11954,7 +11936,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11972,7 +11954,7 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>20</v>
@@ -11983,10 +11965,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12095,10 +12077,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12209,10 +12191,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12325,14 +12307,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12351,16 +12333,16 @@
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12410,7 +12392,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>87</v>
@@ -12425,24 +12407,24 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12468,10 +12450,10 @@
         <v>182</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12501,10 +12483,10 @@
         <v>112</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -12522,7 +12504,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12551,10 +12533,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12577,13 +12559,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12634,7 +12616,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12652,7 +12634,7 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>20</v>
@@ -12663,10 +12645,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12689,16 +12671,16 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12748,7 +12730,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12766,7 +12748,7 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>20</v>
@@ -12777,10 +12759,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12806,13 +12788,13 @@
         <v>235</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12862,7 +12844,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12880,7 +12862,7 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>20</v>
@@ -12891,10 +12873,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13003,10 +12985,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13117,10 +13099,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13233,10 +13215,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13262,10 +13244,10 @@
         <v>154</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13316,7 +13298,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13340,15 +13322,15 @@
         <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13371,13 +13353,13 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13428,7 +13410,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13446,7 +13428,7 @@
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>20</v>
@@ -13457,10 +13439,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13486,10 +13468,10 @@
         <v>182</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13519,10 +13501,10 @@
         <v>112</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -13540,7 +13522,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13558,21 +13540,21 @@
         <v>20</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13598,10 +13580,10 @@
         <v>182</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13628,13 +13610,11 @@
         <v>20</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -13652,7 +13632,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13676,15 +13656,15 @@
         <v>20</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13710,16 +13690,16 @@
         <v>182</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -13744,13 +13724,13 @@
         <v>20</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -13768,7 +13748,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13786,21 +13766,21 @@
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13826,10 +13806,10 @@
         <v>182</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13859,10 +13839,10 @@
         <v>112</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -13880,7 +13860,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13898,21 +13878,21 @@
         <v>20</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13938,10 +13918,10 @@
         <v>182</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13971,10 +13951,10 @@
         <v>112</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -13992,7 +13972,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14010,21 +13990,21 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14047,13 +14027,13 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14104,7 +14084,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14122,21 +14102,21 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14162,10 +14142,10 @@
         <v>182</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14192,13 +14172,13 @@
         <v>20</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>20</v>
@@ -14216,7 +14196,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14234,21 +14214,21 @@
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14274,13 +14254,13 @@
         <v>235</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14330,7 +14310,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14348,7 +14328,7 @@
         <v>20</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>20</v>
@@ -14359,10 +14339,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14471,10 +14451,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14585,10 +14565,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14701,10 +14681,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14727,13 +14707,13 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14784,7 +14764,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>87</v>
@@ -14799,24 +14779,24 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14842,13 +14822,13 @@
         <v>107</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14877,10 +14857,10 @@
         <v>176</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -14898,7 +14878,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14916,7 +14896,7 @@
         <v>20</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>20</v>
@@ -14927,10 +14907,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14956,13 +14936,13 @@
         <v>182</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14988,13 +14968,13 @@
         <v>20</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
@@ -15012,7 +14992,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15041,10 +15021,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15070,10 +15050,10 @@
         <v>210</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15124,7 +15104,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15142,7 +15122,7 @@
         <v>20</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>20</v>
@@ -15153,10 +15133,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15179,13 +15159,13 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15236,7 +15216,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15251,24 +15231,24 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15291,16 +15271,16 @@
         <v>20</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15350,7 +15330,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15365,10 +15345,10 @@
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>20</v>
